--- a/Roadmap.xlsx
+++ b/Roadmap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jaygmgtmgmail.sharepoint.com/sites/Management/Shared Documents/Documentation Repository/METRC API Scripts/live-menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{B3BD4EDA-8903-432C-834F-2564684E2FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44143649-3008-4089-B88C-150A179D5641}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{B3BD4EDA-8903-432C-834F-2564684E2FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{649CA754-6676-44DE-AF76-26DF569A7807}"/>
   <bookViews>
-    <workbookView xWindow="33165" yWindow="2715" windowWidth="24180" windowHeight="11295" xr2:uid="{C91F4BAF-59AF-42FC-911B-353150C79106}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C91F4BAF-59AF-42FC-911B-353150C79106}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -957,7 +957,7 @@
   <cols>
     <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
     <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.1640625" bestFit="1" customWidth="1"/>
@@ -1640,6 +1640,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7C8ACCDA4A9654B9ECAF89C3754D873" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="99ba8e7a8497e31066cec7ac35935a26">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2e1cf8b-a144-4186-a0b6-a70beae60693" xmlns:ns3="867b9853-ea2f-4431-bec1-fb47bf72dfce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0308723e973a6e9a2b32d0a3d9327b86" ns2:_="" ns3:_="">
     <xsd:import namespace="f2e1cf8b-a144-4186-a0b6-a70beae60693"/>
@@ -1834,15 +1843,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1855,13 +1855,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6F6EC69-6D05-4012-B6CB-2B7940591F93}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BD342C-5752-4E4B-A2C9-81570F1E28D1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BD342C-5752-4E4B-A2C9-81570F1E28D1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6F6EC69-6D05-4012-B6CB-2B7940591F93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f2e1cf8b-a144-4186-a0b6-a70beae60693"/>
+    <ds:schemaRef ds:uri="867b9853-ea2f-4431-bec1-fb47bf72dfce"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D1EF49-0E57-4A93-8BB3-7B5366C676B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D1EF49-0E57-4A93-8BB3-7B5366C676B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="867b9853-ea2f-4431-bec1-fb47bf72dfce"/>
+    <ds:schemaRef ds:uri="f2e1cf8b-a144-4186-a0b6-a70beae60693"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Roadmap.xlsx
+++ b/Roadmap.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jaygmgtmgmail.sharepoint.com/sites/Management/Shared Documents/Documentation Repository/METRC API Scripts/live-menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{B3BD4EDA-8903-432C-834F-2564684E2FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{649CA754-6676-44DE-AF76-26DF569A7807}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{B3BD4EDA-8903-432C-834F-2564684E2FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20434781-5819-4430-AB65-313073570BCE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C91F4BAF-59AF-42FC-911B-353150C79106}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="261">
   <si>
     <t>Component</t>
   </si>
@@ -80,21 +80,12 @@
     <t>None</t>
   </si>
   <si>
-    <t>Missing/incorrect keys breaks all API calls</t>
-  </si>
-  <si>
     <t>Excel Downloader</t>
   </si>
   <si>
     <t>Pull pricing + bulk rules from SharePoint</t>
   </si>
   <si>
-    <t>rclone remote: ceres_sharepoint</t>
-  </si>
-  <si>
-    <t>Local /tmp/Product Information.xlsx</t>
-  </si>
-  <si>
     <t>rclone installed</t>
   </si>
   <si>
@@ -110,33 +101,12 @@
     <t>Excel Parser</t>
   </si>
   <si>
-    <t>Map product name → price/type + load bulk rules</t>
-  </si>
-  <si>
-    <t>product_map dict + bulk_rules list</t>
-  </si>
-  <si>
     <t>pandas, openpyxl</t>
   </si>
   <si>
-    <t>Excel sheet names + column names</t>
-  </si>
-  <si>
-    <t>Column rename breaks pricing silently</t>
-  </si>
-  <si>
     <t>Package Puller</t>
   </si>
   <si>
-    <t>Get active METRC packages</t>
-  </si>
-  <si>
-    <t>METRC API /packages/v2/active</t>
-  </si>
-  <si>
-    <t>packages_map dict</t>
-  </si>
-  <si>
     <t>requests</t>
   </si>
   <si>
@@ -146,45 +116,21 @@
     <t>LicenseNumber valid</t>
   </si>
   <si>
-    <t>API failure, auth error, pagination issues</t>
-  </si>
-  <si>
     <t>Room Filter</t>
   </si>
   <si>
-    <t>Limit website inventory to specific rooms</t>
-  </si>
-  <si>
-    <t>LocationName field</t>
-  </si>
-  <si>
     <t>Filtered packages</t>
   </si>
   <si>
-    <t>ROOMS constant</t>
-  </si>
-  <si>
     <t>Misspelled room excludes inventory</t>
   </si>
   <si>
     <t>Lab Puller</t>
   </si>
   <si>
-    <t>Get lab results per package</t>
-  </si>
-  <si>
-    <t>METRC /labtests/v2/results</t>
-  </si>
-  <si>
-    <t>lab_by_pkg dict</t>
-  </si>
-  <si>
     <t>PackageId valid</t>
   </si>
   <si>
-    <t>N+1 calls = slowdown; API rate limits</t>
-  </si>
-  <si>
     <t>JSON Builder</t>
   </si>
   <si>
@@ -203,252 +149,87 @@
     <t>menu.json structure</t>
   </si>
   <si>
-    <t>Field rename breaks frontend</t>
-  </si>
-  <si>
     <t>Change Detector</t>
   </si>
   <si>
-    <t>Prevent unnecessary Git pushes</t>
-  </si>
-  <si>
-    <t>menu.json hash</t>
-  </si>
-  <si>
-    <t>Exit or proceed</t>
-  </si>
-  <si>
     <t>hashlib</t>
   </si>
   <si>
     <t>menu.json</t>
   </si>
   <si>
-    <t>Hash mismatch logic errors</t>
-  </si>
-  <si>
     <t>Git Sync</t>
   </si>
   <si>
-    <t>Pull, write, commit, push</t>
-  </si>
-  <si>
-    <t>Updated JSON</t>
-  </si>
-  <si>
-    <t>menu.json in repo</t>
-  </si>
-  <si>
     <t>git CLI</t>
   </si>
   <si>
     <t>GitHub</t>
   </si>
   <si>
-    <t>GitHub auth valid</t>
-  </si>
-  <si>
-    <t>Token expiration, commit string bug</t>
-  </si>
-  <si>
     <t>Menu Loader</t>
   </si>
   <si>
-    <t>Load live inventory</t>
-  </si>
-  <si>
-    <t>DATA_URL (menu.json)</t>
-  </si>
-  <si>
-    <t>In-memory packages[]</t>
-  </si>
-  <si>
     <t>Browser fetch</t>
   </si>
   <si>
-    <t>GitHub raw URL</t>
-  </si>
-  <si>
-    <t>URL change breaks load</t>
-  </si>
-  <si>
     <t>License Loader</t>
   </si>
   <si>
     <t>Load dispensary autocomplete</t>
   </si>
   <si>
-    <t>LICENSES_URL (licenses.json)</t>
-  </si>
-  <si>
-    <t>licenses[] array</t>
-  </si>
-  <si>
     <t>licenses.json</t>
   </si>
   <si>
-    <t>Malformed JSON breaks autocomplete</t>
-  </si>
-  <si>
     <t>Package Merger</t>
   </si>
   <si>
-    <t>Combine multiple batches per SKU</t>
-  </si>
-  <si>
-    <t>menu.json items</t>
-  </si>
-  <si>
-    <t>Merged packages array</t>
-  </si>
-  <si>
     <t>JS runtime</t>
   </si>
   <si>
-    <t>ItemName field</t>
-  </si>
-  <si>
-    <t>Missing ItemName breaks grouping</t>
-  </si>
-  <si>
     <t>Lab Analyzer</t>
   </si>
   <si>
-    <t>Compute THC/CBD/Terps %</t>
-  </si>
-  <si>
-    <t>LabResults array</t>
-  </si>
-  <si>
-    <t>analytes object</t>
-  </si>
-  <si>
-    <t>TestTypeName format</t>
-  </si>
-  <si>
-    <t>Changed lab names break calc</t>
-  </si>
-  <si>
     <t>Group Classifier</t>
   </si>
   <si>
-    <t>Assign products to sections</t>
-  </si>
-  <si>
-    <t>ItemName string</t>
-  </si>
-  <si>
-    <t>Grouped object</t>
-  </si>
-  <si>
-    <t>Naming conventions</t>
-  </si>
-  <si>
-    <t>Name change misclassifies products</t>
-  </si>
-  <si>
     <t>Renderer</t>
   </si>
   <si>
-    <t>Build HTML tables dynamically</t>
-  </si>
-  <si>
     <t>grouped data</t>
   </si>
   <si>
-    <t>Rendered tables</t>
-  </si>
-  <si>
     <t>DOM</t>
   </si>
   <si>
-    <t>menu-data div</t>
-  </si>
-  <si>
-    <t>Malformed data breaks layout</t>
-  </si>
-  <si>
     <t>Step Enforcer</t>
   </si>
   <si>
-    <t>Round quantities to multiples of 5</t>
-  </si>
-  <si>
     <t>user input</t>
   </si>
   <si>
-    <t>Clean quantity value</t>
-  </si>
-  <si>
-    <t>data-step attr</t>
-  </si>
-  <si>
-    <t>Non-numeric input issues</t>
-  </si>
-  <si>
     <t>Totals Engine</t>
   </si>
   <si>
-    <t>Calculate line totals + running total</t>
-  </si>
-  <si>
     <t>price × qty</t>
   </si>
   <si>
-    <t>Displayed total</t>
-  </si>
-  <si>
-    <t>item-price data attr</t>
-  </si>
-  <si>
-    <t>Missing data-price breaks totals</t>
-  </si>
-  <si>
     <t>Order Builder</t>
   </si>
   <si>
-    <t>Create HTML + JSON order</t>
-  </si>
-  <si>
-    <t>object model</t>
-  </si>
-  <si>
-    <t>Email payload</t>
-  </si>
-  <si>
-    <t>DOM structure</t>
-  </si>
-  <si>
-    <t>Selector changes break build</t>
-  </si>
-  <si>
     <t>Email Sender</t>
   </si>
   <si>
     <t>Send order via EmailJS</t>
   </si>
   <si>
-    <t>service ID, template ID</t>
-  </si>
-  <si>
-    <t>Email + JSON attachment</t>
-  </si>
-  <si>
     <t>EmailJS SDK</t>
   </si>
   <si>
-    <t>EmailJS service</t>
-  </si>
-  <si>
-    <t>Account limits, template mismatch</t>
-  </si>
-  <si>
     <t>Iframe Resizer</t>
   </si>
   <si>
-    <t>Auto-fit inside Squarespace</t>
-  </si>
-  <si>
     <t>wrapper height</t>
   </si>
   <si>
@@ -458,82 +239,25 @@
     <t>Browser API</t>
   </si>
   <si>
-    <t>Squarespace parent page</t>
-  </si>
-  <si>
-    <t>Parent listener</t>
-  </si>
-  <si>
-    <t>Parent not listening = scroll issues</t>
-  </si>
-  <si>
-    <t>Field Name</t>
-  </si>
-  <si>
     <t>Required By</t>
   </si>
   <si>
-    <t>Reason</t>
-  </si>
-  <si>
     <t>ItemName</t>
   </si>
   <si>
-    <t>Frontend grouping + rendering</t>
-  </si>
-  <si>
-    <t>Product display &amp; classification</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Display + totals</t>
-  </si>
-  <si>
-    <t>Inventory shown</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
-    <t>Totals engine</t>
-  </si>
-  <si>
-    <t>Order calculation</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Category column</t>
-  </si>
-  <si>
-    <t>Display grouping</t>
-  </si>
-  <si>
     <t>LabResults</t>
   </si>
   <si>
-    <t>Lab analyzer</t>
-  </si>
-  <si>
-    <t>THC/CBD/Terps calc</t>
-  </si>
-  <si>
     <t>bulkRules</t>
-  </si>
-  <si>
-    <t>Future pricing logic</t>
-  </si>
-  <si>
-    <t>Bulk discount display</t>
-  </si>
-  <si>
-    <t>CRITICAL CROSS-SYSTEM CONTRACT</t>
-  </si>
-  <si>
-    <t>These fields MUST match between Python and Frontend:</t>
   </si>
   <si>
     <t>Python Inventory Publisher (update_menu_automator.py)</t>
@@ -552,12 +276,662 @@
   });
 &lt;/script&gt;</t>
   </si>
+  <si>
+    <t>Missing keys break API calls</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">rclone remote </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ceres_sharepoint:Product Information.xlsx</t>
+    </r>
+  </si>
+  <si>
+    <t>/tmp/Product Information.xlsx</t>
+  </si>
+  <si>
+    <t>Map product → price/type + load bulk rules</t>
+  </si>
+  <si>
+    <r>
+      <t>product_map</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>bulk_rules</t>
+    </r>
+  </si>
+  <si>
+    <t>Excel sheet names + columns</t>
+  </si>
+  <si>
+    <t>Column rename breaks pricing</t>
+  </si>
+  <si>
+    <t>Retrieve active METRC packages</t>
+  </si>
+  <si>
+    <t>/packages/v2/active</t>
+  </si>
+  <si>
+    <r>
+      <t>packages_map</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dict</t>
+    </r>
+  </si>
+  <si>
+    <t>API failure, auth errors</t>
+  </si>
+  <si>
+    <t>Limit website inventory to allowed rooms</t>
+  </si>
+  <si>
+    <t>LocationName</t>
+  </si>
+  <si>
+    <r>
+      <t>ROOMS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> constant</t>
+    </r>
+  </si>
+  <si>
+    <t>Lab Cache Loader</t>
+  </si>
+  <si>
+    <t>Load locally cached lab results</t>
+  </si>
+  <si>
+    <t>/home/ceres/cache/lab_results_cache.json</t>
+  </si>
+  <si>
+    <r>
+      <t>lab_cache</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dict</t>
+    </r>
+  </si>
+  <si>
+    <t>Python filesystem</t>
+  </si>
+  <si>
+    <t>lab_results_cache.json</t>
+  </si>
+  <si>
+    <t>Corrupt JSON breaks load</t>
+  </si>
+  <si>
+    <t>Pull lab results only for new packages</t>
+  </si>
+  <si>
+    <t>/labtests/v2/results</t>
+  </si>
+  <si>
+    <r>
+      <t>lab_by_pkg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> dict</t>
+    </r>
+  </si>
+  <si>
+    <t>API failure, rate limits</t>
+  </si>
+  <si>
+    <t>Lab Filter</t>
+  </si>
+  <si>
+    <t>Limit results to THC/CBD/terpenes</t>
+  </si>
+  <si>
+    <t>filtered analytes</t>
+  </si>
+  <si>
+    <t>Python runtime</t>
+  </si>
+  <si>
+    <t>ANALYTES list</t>
+  </si>
+  <si>
+    <t>Changed test names break match</t>
+  </si>
+  <si>
+    <t>Lab Cache Updater</t>
+  </si>
+  <si>
+    <t>Save new lab results locally</t>
+  </si>
+  <si>
+    <t>new results</t>
+  </si>
+  <si>
+    <t>updated cache file</t>
+  </si>
+  <si>
+    <t>write permission issues</t>
+  </si>
+  <si>
+    <t>Cache Cleaner</t>
+  </si>
+  <si>
+    <t>Remove labs for packages no longer in inventory</t>
+  </si>
+  <si>
+    <t>packages_map</t>
+  </si>
+  <si>
+    <t>cleaned cache</t>
+  </si>
+  <si>
+    <t>cache file</t>
+  </si>
+  <si>
+    <t>stale data if skipped</t>
+  </si>
+  <si>
+    <t>packages_map + excel_map + lab_by_pkg</t>
+  </si>
+  <si>
+    <t>field rename breaks frontend</t>
+  </si>
+  <si>
+    <t>JSON Serializer</t>
+  </si>
+  <si>
+    <t>Convert payload → compact JSON</t>
+  </si>
+  <si>
+    <t>payload</t>
+  </si>
+  <si>
+    <t>encoding errors</t>
+  </si>
+  <si>
+    <t>Prevent unnecessary repo pushes</t>
+  </si>
+  <si>
+    <t>old hash vs new hash</t>
+  </si>
+  <si>
+    <t>exit or proceed</t>
+  </si>
+  <si>
+    <t>logic bug causes missed updates</t>
+  </si>
+  <si>
+    <t>Pull repo before writing JSON</t>
+  </si>
+  <si>
+    <t>git repo</t>
+  </si>
+  <si>
+    <t>updated working tree</t>
+  </si>
+  <si>
+    <t>repo path</t>
+  </si>
+  <si>
+    <t>merge conflicts</t>
+  </si>
+  <si>
+    <t>Git Commit</t>
+  </si>
+  <si>
+    <t>Record menu update</t>
+  </si>
+  <si>
+    <t>local commit</t>
+  </si>
+  <si>
+    <t>commit metadata</t>
+  </si>
+  <si>
+    <t>empty commit</t>
+  </si>
+  <si>
+    <t>Pages Build Guard</t>
+  </si>
+  <si>
+    <t>Prevent push while GitHub Pages build running</t>
+  </si>
+  <si>
+    <t>gh run list</t>
+  </si>
+  <si>
+    <t>skip push or proceed</t>
+  </si>
+  <si>
+    <t>gh CLI</t>
+  </si>
+  <si>
+    <t>GitHub Actions</t>
+  </si>
+  <si>
+    <t>GH auth</t>
+  </si>
+  <si>
+    <t>gh CLI missing</t>
+  </si>
+  <si>
+    <t>Git Push</t>
+  </si>
+  <si>
+    <t>Publish updated menu.json</t>
+  </si>
+  <si>
+    <t>repo commit</t>
+  </si>
+  <si>
+    <t>GitHub repo</t>
+  </si>
+  <si>
+    <t>GitHub auth</t>
+  </si>
+  <si>
+    <t>token expiration</t>
+  </si>
+  <si>
+    <t>Runtime Data Objects</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Created By</t>
+  </si>
+  <si>
+    <t>excel_map</t>
+  </si>
+  <si>
+    <t>product → price/type mapping</t>
+  </si>
+  <si>
+    <t>bulk_rules</t>
+  </si>
+  <si>
+    <t>bulk pricing tiers</t>
+  </si>
+  <si>
+    <t>inventory snapshot</t>
+  </si>
+  <si>
+    <t>lab_cache</t>
+  </si>
+  <si>
+    <t>cached package lab results</t>
+  </si>
+  <si>
+    <t>lab_by_pkg</t>
+  </si>
+  <si>
+    <t>labs used for this run</t>
+  </si>
+  <si>
+    <t>final menu dataset</t>
+  </si>
+  <si>
+    <t>Cache System</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>{
+  "PackageId": [
+    {"TestTypeName":"THC","TestResultLevel":"21.5"}
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Behavior</t>
+  </si>
+  <si>
+    <t>Run Type</t>
+  </si>
+  <si>
+    <t>Lab Calls</t>
+  </si>
+  <si>
+    <t>Cache Change</t>
+  </si>
+  <si>
+    <t>First run</t>
+  </si>
+  <si>
+    <t>N packages</t>
+  </si>
+  <si>
+    <t>cache populated</t>
+  </si>
+  <si>
+    <t>Normal runs</t>
+  </si>
+  <si>
+    <t>cache reused</t>
+  </si>
+  <si>
+    <t>New package appears</t>
+  </si>
+  <si>
+    <t>cache updated</t>
+  </si>
+  <si>
+    <t>Package removed</t>
+  </si>
+  <si>
+    <t>cache cleaned</t>
+  </si>
+  <si>
+    <t>JSON Output Contract</t>
+  </si>
+  <si>
+    <t>Produced file:</t>
+  </si>
+  <si>
+    <t>Structure:</t>
+  </si>
+  <si>
+    <t>Item fields:</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>METRC package</t>
+  </si>
+  <si>
+    <t>Label</t>
+  </si>
+  <si>
+    <t>METRC</t>
+  </si>
+  <si>
+    <t>Excel ProductInfo</t>
+  </si>
+  <si>
+    <t>METRC lab results</t>
+  </si>
+  <si>
+    <t>{
+  "items": [...],
+  "bulkRules": [...]
+}</t>
+  </si>
+  <si>
+    <t>Dependencies</t>
+  </si>
+  <si>
+    <t>Fetch inventory JSON</t>
+  </si>
+  <si>
+    <t>DATA_URL</t>
+  </si>
+  <si>
+    <t>packages[]</t>
+  </si>
+  <si>
+    <t>licenses[]</t>
+  </si>
+  <si>
+    <t>Merge batches by ItemName</t>
+  </si>
+  <si>
+    <t>merged packages</t>
+  </si>
+  <si>
+    <t>Calculate THC/CBD/Terpenes</t>
+  </si>
+  <si>
+    <t>analyte totals</t>
+  </si>
+  <si>
+    <t>Categorize products</t>
+  </si>
+  <si>
+    <t>Build HTML menu tables</t>
+  </si>
+  <si>
+    <t>DOM tables</t>
+  </si>
+  <si>
+    <t>Force quantity multiples</t>
+  </si>
+  <si>
+    <t>normalized qty</t>
+  </si>
+  <si>
+    <t>Calculate line totals</t>
+  </si>
+  <si>
+    <t>displayed totals</t>
+  </si>
+  <si>
+    <t>Build order JSON</t>
+  </si>
+  <si>
+    <t>DOM selections</t>
+  </si>
+  <si>
+    <t>order payload</t>
+  </si>
+  <si>
+    <t>email + JSON</t>
+  </si>
+  <si>
+    <t>Resize Squarespace iframe</t>
+  </si>
+  <si>
+    <t>Component Architecture</t>
+  </si>
+  <si>
+    <t>Cross-System Contract (Critical)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fields that </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>must match between Python and Frontend</t>
+    </r>
+  </si>
+  <si>
+    <t>frontend grouping</t>
+  </si>
+  <si>
+    <t>product display</t>
+  </si>
+  <si>
+    <t>totals engine</t>
+  </si>
+  <si>
+    <t>inventory display</t>
+  </si>
+  <si>
+    <t>order calculation</t>
+  </si>
+  <si>
+    <t>category grouping</t>
+  </si>
+  <si>
+    <t>menu layout</t>
+  </si>
+  <si>
+    <t>lab analyzer</t>
+  </si>
+  <si>
+    <t>THC/CBD/Terp calc</t>
+  </si>
+  <si>
+    <t>future pricing logic</t>
+  </si>
+  <si>
+    <t>bulk discount</t>
+  </si>
+  <si>
+    <t>Current Performance Characteristics</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>Before Cache</t>
+  </si>
+  <si>
+    <t>After Cache</t>
+  </si>
+  <si>
+    <t>Lab API calls</t>
+  </si>
+  <si>
+    <t>N per run</t>
+  </si>
+  <si>
+    <t>0 per run</t>
+  </si>
+  <si>
+    <t>Script runtime</t>
+  </si>
+  <si>
+    <t>30–90 sec</t>
+  </si>
+  <si>
+    <t>2–5 sec</t>
+  </si>
+  <si>
+    <t>METRC load</t>
+  </si>
+  <si>
+    <t>heavy</t>
+  </si>
+  <si>
+    <t>minimal</t>
+  </si>
+  <si>
+    <t>Next Planned Improvements</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Improvement</t>
+  </si>
+  <si>
+    <t>Benefit</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Add request retry logic</t>
+  </si>
+  <si>
+    <t>avoid transient METRC failures</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Add API throttling delay</t>
+  </si>
+  <si>
+    <t>prevent 429 errors</t>
+  </si>
+  <si>
+    <t>Add schema validation for menu.json</t>
+  </si>
+  <si>
+    <t>prevent frontend breakage</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Precompile product grouping</t>
+  </si>
+  <si>
+    <t>faster frontend rendering</t>
+  </si>
+  <si>
+    <t>Metrics logging for script runtime</t>
+  </si>
+  <si>
+    <t>easier debugging</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="9"/>
       <color theme="1"/>
@@ -575,7 +949,36 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -608,15 +1011,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -952,8 +1384,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B217A18-2D12-4D15-AEB5-08E3EFFD4184}">
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H99"/>
+  <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
@@ -963,14 +1395,22 @@
     <col min="6" max="6" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="30.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="21.75" customHeight="1">
+      <c r="A1" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" ht="24">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -996,645 +1436,1145 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8" ht="12.75">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="37.5">
+      <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+    </row>
+    <row r="5" spans="1:8" ht="12.75">
+      <c r="A5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="12.75">
+      <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="B6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="G6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H6" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="12.75">
+      <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="F7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+    <row r="8" spans="1:8" ht="25.5">
+      <c r="A8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="12.75">
+      <c r="A9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" t="s">
+      <c r="H9" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="24">
+      <c r="A11" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="24">
+      <c r="A13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
+      <c r="B13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" t="s">
+      <c r="C13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G6" t="s">
+      <c r="E14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="F14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C7" t="s">
+      <c r="F15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D7" t="s">
+      <c r="H15" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E7" t="s">
+      <c r="B16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="G17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="12.75">
+      <c r="A18" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H7" t="s">
+      <c r="F19" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="G19" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="31.5">
+      <c r="A23" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="12.75">
+      <c r="A25" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="12.75">
+      <c r="A26" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="25.5">
+      <c r="A27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="12.75">
+      <c r="A28" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="12.75">
+      <c r="A29" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="12.75">
+      <c r="A30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="31.5">
+      <c r="A35" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="F35" s="8" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="F36" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="18.75">
+      <c r="A37" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="7"/>
+      <c r="F38" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="24">
+      <c r="A39" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="F40" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="18.75">
+      <c r="A41" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="12.75">
+      <c r="A43" s="9"/>
+    </row>
+    <row r="44" spans="1:8" ht="18.75">
+      <c r="A44" s="11" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="24">
+      <c r="A49" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B49" s="3">
+        <v>1</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="31.5">
+      <c r="A53" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="B53" s="10"/>
+      <c r="C53" s="10"/>
+    </row>
+    <row r="55" spans="1:3" ht="15">
+      <c r="A55" s="12" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="7"/>
+    </row>
+    <row r="57" spans="1:3" ht="12.75">
+      <c r="A57" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15">
+      <c r="A59" s="12" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15">
+      <c r="A62" s="12" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="36.75" customHeight="1">
+      <c r="A74" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="21">
+      <c r="A75" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B75" s="13"/>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B77" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E77" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D8" t="s">
+      <c r="B78" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E8" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" t="s">
+      <c r="C78" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H8" t="s">
+      <c r="D78" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B79" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B9" t="s">
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="s">
+      <c r="B80" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D9" t="s">
+      <c r="B81" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E9" t="s">
+      <c r="B82" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C82" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" t="s">
+      <c r="D82" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E82" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H9" t="s">
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B83" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C83" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D83" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B84" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D84" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E10" t="s">
+      <c r="B85" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="B86" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H10" t="s">
+      <c r="C86" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E86" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
+    <row r="87" spans="1:5">
+      <c r="A87" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B87" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C87" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D87" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E87" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="90" spans="1:5" ht="31.5">
+      <c r="A90" s="8" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F11" t="s">
+      <c r="C93" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G11" t="s">
+      <c r="B94" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H11" t="s">
+      <c r="B95" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
+      <c r="B96" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B97" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B98" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F17" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" t="s">
-        <v>75</v>
-      </c>
-      <c r="F18" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" t="s">
-        <v>89</v>
-      </c>
-      <c r="H19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" t="s">
-        <v>92</v>
-      </c>
-      <c r="C20" t="s">
-        <v>93</v>
-      </c>
-      <c r="D20" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" t="s">
-        <v>88</v>
-      </c>
-      <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" t="s">
-        <v>95</v>
-      </c>
-      <c r="H20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" t="s">
-        <v>101</v>
-      </c>
-      <c r="H21" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>103</v>
-      </c>
-      <c r="B22" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" t="s">
-        <v>107</v>
-      </c>
-      <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" t="s">
-        <v>108</v>
-      </c>
-      <c r="H22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>110</v>
-      </c>
-      <c r="B23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>113</v>
-      </c>
-      <c r="E23" t="s">
-        <v>88</v>
-      </c>
-      <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" t="s">
-        <v>114</v>
-      </c>
-      <c r="H23" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" t="s">
-        <v>119</v>
-      </c>
-      <c r="E24" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>122</v>
-      </c>
-      <c r="B25" t="s">
-        <v>123</v>
-      </c>
-      <c r="C25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D25" t="s">
-        <v>125</v>
-      </c>
-      <c r="E25" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" t="s">
-        <v>126</v>
-      </c>
-      <c r="H25" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>128</v>
-      </c>
-      <c r="B26" t="s">
-        <v>129</v>
-      </c>
-      <c r="C26" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" t="s">
-        <v>131</v>
-      </c>
-      <c r="E26" t="s">
-        <v>132</v>
-      </c>
-      <c r="F26" t="s">
-        <v>133</v>
-      </c>
-      <c r="G26" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>135</v>
-      </c>
-      <c r="B27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" t="s">
-        <v>138</v>
-      </c>
-      <c r="E27" t="s">
-        <v>139</v>
-      </c>
-      <c r="F27" t="s">
-        <v>140</v>
-      </c>
-      <c r="G27" t="s">
-        <v>141</v>
-      </c>
-      <c r="H27" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="24" x14ac:dyDescent="0.4">
-      <c r="A29" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="24" x14ac:dyDescent="0.4">
-      <c r="A30" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>146</v>
-      </c>
-      <c r="B32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C32" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>149</v>
-      </c>
-      <c r="B33" t="s">
-        <v>150</v>
-      </c>
-      <c r="C33" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>155</v>
-      </c>
-      <c r="B35" t="s">
-        <v>156</v>
-      </c>
-      <c r="C35" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>158</v>
-      </c>
-      <c r="B36" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>161</v>
-      </c>
-      <c r="B37" t="s">
-        <v>162</v>
-      </c>
-      <c r="C37" t="s">
-        <v>163</v>
+      <c r="B99" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A35:C35"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="F23:H23"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Roadmap.xlsx
+++ b/Roadmap.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jaygmgtmgmail.sharepoint.com/sites/Management/Shared Documents/Documentation Repository/METRC API Scripts/live-menu/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{B3BD4EDA-8903-432C-834F-2564684E2FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20434781-5819-4430-AB65-313073570BCE}"/>
+  <xr:revisionPtr revIDLastSave="178" documentId="8_{B3BD4EDA-8903-432C-834F-2564684E2FEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{778F8558-AB2C-475D-9631-E6DE89A63FD0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C91F4BAF-59AF-42FC-911B-353150C79106}"/>
+    <workbookView xWindow="29145" yWindow="750" windowWidth="28260" windowHeight="14250" xr2:uid="{C91F4BAF-59AF-42FC-911B-353150C79106}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="291">
   <si>
     <t>Component</t>
   </si>
@@ -925,6 +925,96 @@
   </si>
   <si>
     <t>easier debugging</t>
+  </si>
+  <si>
+    <t>Main information Sources</t>
+  </si>
+  <si>
+    <t>Product information master</t>
+  </si>
+  <si>
+    <t>Info Type</t>
+  </si>
+  <si>
+    <t>Updated By</t>
+  </si>
+  <si>
+    <t>Sends Updates To:</t>
+  </si>
+  <si>
+    <t>OneDrive - Ceres Naturals\Management - Documents\Documentation Repository\zMaster Office Documents\Product Information\Product Information Master.xlsx</t>
+  </si>
+  <si>
+    <t>Manual</t>
+  </si>
+  <si>
+    <t>OneDrive - Ceres Naturals\Ceres Public Share - Documents\METRC API Depot - Via power Automate Cloud</t>
+  </si>
+  <si>
+    <t>Dispensaries Address Data</t>
+  </si>
+  <si>
+    <t>OneDrive - Ceres Naturals\Sales and Marketing - Documents\Sales\Dispensaries Address Data.xlsx</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>contains, price, type, description, bulk price rules, strain, etc.</t>
+  </si>
+  <si>
+    <t>contains license data, addresses, credit iformation, AP contact information</t>
+  </si>
+  <si>
+    <t>Used By:</t>
+  </si>
+  <si>
+    <t>update_menu_automator.py / other?</t>
+  </si>
+  <si>
+    <t>update_menu_automator.py / invoice maker</t>
+  </si>
+  <si>
+    <t>Automated Scripts</t>
+  </si>
+  <si>
+    <t>Script Name</t>
+  </si>
+  <si>
+    <t>files it touches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">update_menu_automator.py </t>
+  </si>
+  <si>
+    <t>ceres automator macine</t>
+  </si>
+  <si>
+    <t>outputs</t>
+  </si>
+  <si>
+    <t>menu.json/other?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dispensaries address data, product information master, menu.json, </t>
+  </si>
+  <si>
+    <t>Menu.json</t>
+  </si>
+  <si>
+    <t>C:\Users\somet\OneDrive - Ceres Naturals\Management - Documents\Documentation Repository\METRC API Scripts\live-menu\menu.json</t>
+  </si>
+  <si>
+    <t>update_menu_automator.py</t>
+  </si>
+  <si>
+    <t>website</t>
+  </si>
+  <si>
+    <t>contains all data to populate menu on website, website call this file from github</t>
   </si>
 </sst>
 </file>
@@ -1011,7 +1101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1026,9 +1116,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1040,16 +1127,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1384,11 +1475,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B217A18-2D12-4D15-AEB5-08E3EFFD4184}">
-  <dimension ref="A1:H99"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="38.33203125" customWidth="1"/>
     <col min="3" max="3" width="26.1640625" customWidth="1"/>
     <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -1398,1182 +1489,1301 @@
     <col min="11" max="11" width="28.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="21.75" customHeight="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>286</v>
+      </c>
+      <c r="B5" t="s">
+        <v>287</v>
+      </c>
+      <c r="C5" t="s">
+        <v>288</v>
+      </c>
+      <c r="D5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" t="s">
+        <v>283</v>
+      </c>
+      <c r="D8" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>281</v>
+      </c>
+      <c r="B9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="14" customFormat="1"/>
+    <row r="14" spans="1:8" ht="21.75" customHeight="1">
+      <c r="A14" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-    </row>
-    <row r="2" spans="1:8" ht="24">
-      <c r="A2" s="2" t="s">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="11"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" ht="24">
+      <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="12.75">
-      <c r="A3" s="3" t="s">
+    <row r="16" spans="1:8" ht="12.75">
+      <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="37.5">
-      <c r="A4" s="3" t="s">
+    <row r="17" spans="1:8" ht="37.5">
+      <c r="A17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D17" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="12.75">
-      <c r="A5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="12.75">
-      <c r="A6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="12.75">
-      <c r="A7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="25.5">
-      <c r="A8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="12.75">
-      <c r="A9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="24">
-      <c r="A11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="24">
-      <c r="A13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="12.75">
       <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="12.75">
+      <c r="A19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="12.75">
+      <c r="A20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="25.5">
+      <c r="A21" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="12.75">
+      <c r="A22" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="24">
+      <c r="A24" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="24">
+      <c r="A26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="12.75">
+      <c r="A31" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B31" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F31" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="G31" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H31" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="3" t="s">
+    <row r="32" spans="1:8">
+      <c r="A32" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C32" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="H32" s="3" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="31.5">
-      <c r="A23" s="5" t="s">
+    <row r="36" spans="1:8" ht="31.5">
+      <c r="A36" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="10" t="s">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="2" t="s">
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B37" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C37" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="H37" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="12.75">
-      <c r="A25" s="4" t="s">
+    <row r="38" spans="1:8" ht="12.75">
+      <c r="A38" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B38" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G38" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H38" s="3" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="12.75">
-      <c r="A26" s="4" t="s">
+    <row r="39" spans="1:8" ht="12.75">
+      <c r="A39" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B39" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C39" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F39" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="G39" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="H39" s="3" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="25.5">
-      <c r="A27" s="4" t="s">
+    <row r="40" spans="1:8" ht="25.5">
+      <c r="A40" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B40" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C40" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F40" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="G40" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="H40" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="12.75">
-      <c r="A28" s="4" t="s">
+    <row r="41" spans="1:8" ht="12.75">
+      <c r="A41" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B41" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C41" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="12.75">
-      <c r="A29" s="4" t="s">
+    <row r="42" spans="1:8" ht="12.75">
+      <c r="A42" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B42" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C42" s="3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="12.75">
-      <c r="A30" s="4" t="s">
+    <row r="43" spans="1:8" ht="12.75">
+      <c r="A43" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B43" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="31.5">
-      <c r="A35" s="10" t="s">
+    <row r="48" spans="1:8" ht="31.5">
+      <c r="A48" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="F35" s="8" t="s">
+      <c r="B48" s="12"/>
+      <c r="C48" s="12"/>
+      <c r="F48" s="7" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
-      <c r="F36" s="2" t="s">
+    <row r="49" spans="1:8">
+      <c r="F49" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G49" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H49" s="2" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="18.75">
-      <c r="A37" s="11" t="s">
+    <row r="50" spans="1:8" ht="18.75">
+      <c r="A50" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F37" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
-      <c r="A38" s="7"/>
-      <c r="F38" s="3" t="s">
+    <row r="51" spans="1:8">
+      <c r="A51" s="6"/>
+      <c r="F51" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="24">
-      <c r="A39" s="9" t="s">
+    <row r="52" spans="1:8" ht="24">
+      <c r="A52" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F39" s="3" t="s">
+      <c r="F52" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G52" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
-      <c r="F40" s="3" t="s">
+    <row r="53" spans="1:8">
+      <c r="F53" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G40" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="H40" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="18.75">
-      <c r="A41" s="11" t="s">
+    <row r="54" spans="1:8" ht="18.75">
+      <c r="A54" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F41" s="3" t="s">
+      <c r="F54" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="G54" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
-      <c r="A42" s="7" t="s">
+    <row r="55" spans="1:8">
+      <c r="A55" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="12.75">
-      <c r="A43" s="9"/>
-    </row>
-    <row r="44" spans="1:8" ht="18.75">
-      <c r="A44" s="11" t="s">
+    <row r="56" spans="1:8" ht="12.75">
+      <c r="A56" s="8"/>
+    </row>
+    <row r="57" spans="1:8" ht="18.75">
+      <c r="A57" s="9" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
-      <c r="A46" s="2" t="s">
+    <row r="59" spans="1:8">
+      <c r="A59" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
-      <c r="A47" s="3" t="s">
+    <row r="60" spans="1:8">
+      <c r="A60" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B60" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
-      <c r="A48" s="3" t="s">
+    <row r="61" spans="1:8">
+      <c r="A61" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B48" s="3">
+      <c r="B61" s="3">
         <v>0</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="24">
-      <c r="A49" s="3" t="s">
+    <row r="62" spans="1:8" ht="24">
+      <c r="A62" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B49" s="3">
+      <c r="B62" s="3">
         <v>1</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="3" t="s">
+    <row r="63" spans="1:8">
+      <c r="A63" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B50" s="3">
+      <c r="B63" s="3">
         <v>0</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="31.5">
-      <c r="A53" s="10" t="s">
+    <row r="66" spans="1:3" ht="31.5">
+      <c r="A66" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="B53" s="10"/>
-      <c r="C53" s="10"/>
-    </row>
-    <row r="55" spans="1:3" ht="15">
-      <c r="A55" s="12" t="s">
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+    </row>
+    <row r="68" spans="1:3" ht="15">
+      <c r="A68" s="10" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="56" spans="1:3">
-      <c r="A56" s="7"/>
-    </row>
-    <row r="57" spans="1:3" ht="12.75">
-      <c r="A57" s="9" t="s">
+    <row r="69" spans="1:3">
+      <c r="A69" s="6"/>
+    </row>
+    <row r="70" spans="1:3" ht="12.75">
+      <c r="A70" s="8" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15">
-      <c r="A59" s="12" t="s">
+    <row r="72" spans="1:3" ht="15">
+      <c r="A72" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="60" spans="1:3">
-      <c r="A60" s="7" t="s">
+    <row r="73" spans="1:3">
+      <c r="A73" s="6" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15">
-      <c r="A62" s="12" t="s">
+    <row r="75" spans="1:3" ht="15">
+      <c r="A75" s="10" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="2" t="s">
+    <row r="77" spans="1:3">
+      <c r="A77" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B77" s="2" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
+    <row r="78" spans="1:3">
+      <c r="A78" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B78" s="3" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="3" t="s">
+    <row r="79" spans="1:3">
+      <c r="A79" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B79" s="3" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="3" t="s">
+    <row r="80" spans="1:3">
+      <c r="A80" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B80" s="3" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="36.75" customHeight="1">
-      <c r="A74" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74" s="10"/>
-      <c r="C74" s="10"/>
-      <c r="D74" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" ht="21">
-      <c r="A75" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="B75" s="13"/>
-    </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="3" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>49</v>
+        <v>192</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>54</v>
+        <v>193</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>49</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="E84" s="3" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="36.75" customHeight="1">
+      <c r="A87" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="21">
+      <c r="A88" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="B88" s="13"/>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E92" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E85" s="3" t="s">
+    <row r="93" spans="1:5">
+      <c r="A93" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
-      <c r="A86" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
-      <c r="A87" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="31.5">
-      <c r="A90" s="8" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
-      <c r="A92" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
-      <c r="A93" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C94" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B94" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C94" s="3" t="s">
-        <v>221</v>
+      <c r="D94" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="3" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>223</v>
+        <v>53</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="31.5">
+      <c r="A103" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B96" s="3" t="s">
+      <c r="B109" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C96" s="3" t="s">
+      <c r="C109" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="97" spans="1:3">
-      <c r="A97" s="3" t="s">
+    <row r="110" spans="1:5">
+      <c r="A110" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B97" s="3" t="s">
+      <c r="B110" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C97" s="3" t="s">
+      <c r="C110" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="98" spans="1:3">
-      <c r="A98" s="3" t="s">
+    <row r="111" spans="1:5">
+      <c r="A111" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B98" s="3" t="s">
+      <c r="B111" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C98" s="3" t="s">
+      <c r="C111" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="99" spans="1:3">
-      <c r="A99" s="3" t="s">
+    <row r="112" spans="1:5">
+      <c r="A112" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="B112" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="C99" s="3" t="s">
+      <c r="C112" s="3" t="s">
         <v>230</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A53:C53"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="F36:H36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2589,6 +2799,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="867b9853-ea2f-4431-bec1-fb47bf72dfce" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2e1cf8b-a144-4186-a0b6-a70beae60693">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A7C8ACCDA4A9654B9ECAF89C3754D873" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="99ba8e7a8497e31066cec7ac35935a26">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2e1cf8b-a144-4186-a0b6-a70beae60693" xmlns:ns3="867b9853-ea2f-4431-bec1-fb47bf72dfce" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0308723e973a6e9a2b32d0a3d9327b86" ns2:_="" ns3:_="">
     <xsd:import namespace="f2e1cf8b-a144-4186-a0b6-a70beae60693"/>
@@ -2783,17 +3004,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="867b9853-ea2f-4431-bec1-fb47bf72dfce" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2e1cf8b-a144-4186-a0b6-a70beae60693">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3BD342C-5752-4E4B-A2C9-81570F1E28D1}">
   <ds:schemaRefs>
@@ -2803,6 +3013,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D1EF49-0E57-4A93-8BB3-7B5366C676B1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="867b9853-ea2f-4431-bec1-fb47bf72dfce"/>
+    <ds:schemaRef ds:uri="f2e1cf8b-a144-4186-a0b6-a70beae60693"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E6F6EC69-6D05-4012-B6CB-2B7940591F93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2819,15 +3040,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5D1EF49-0E57-4A93-8BB3-7B5366C676B1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="867b9853-ea2f-4431-bec1-fb47bf72dfce"/>
-    <ds:schemaRef ds:uri="f2e1cf8b-a144-4186-a0b6-a70beae60693"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>